--- a/docs/박유진_분식집키오스크_작업일지.xlsx
+++ b/docs/박유진_분식집키오스크_작업일지.xlsx
@@ -1,41 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="요약" sheetId="1" r:id="rId1"/>
-    <sheet name="날짜별 작업일지" sheetId="2" r:id="rId2"/>
-    <sheet name="근거 및 참고" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="날짜별 작업일지" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근거 및 참고" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'날짜별 작업일지'!$A$3:$C$18</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <name val="맑은 고딕"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="18"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
       <color rgb="FF555555"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -53,12 +58,44 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FFD9D9D9"/>
       </right>
@@ -73,40 +110,399 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="85" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -119,7 +515,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 박유진 | 기간: 2026-07-13 ~ 2026-08-07</t>
+          <t>담당자: 박유진 | 기간: 2026-07-13 ~ 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -136,38 +532,38 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>총 커밋</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>83건</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>89건</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>작업 기간</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13 ~ 2026-08-07 (26일)</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13 ~ 2026-08-12 (31일)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>활동일</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>15일</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>17일</t>
         </is>
       </c>
     </row>
@@ -184,83 +580,86 @@
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>고객용 키오스크 프론트엔드</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>홈·메뉴선택·장바구니·결제·주문완료 5개 화면 구현 및 디자인, 다국어(한/영)·반응형 대응</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>결제 연동</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>네이버페이·카카오페이·토스페이 결제창 연동, 결제 오류 유형별 처리·자동 재시도, 결제 아키텍처 분리 대응</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>장바구니·주문 로직</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>수량 합산, 총액 계산 함수화, 빈 장바구니/빈 주문목록 안내 및 진입 차단, 90초 자동 초기화</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>메뉴·세트 옵션</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>메뉴·옵션 품절 처리, 세트 메뉴 구성품 품절 연동, 그룹 선택형 세트 메뉴 및 떡순튀세트 옵션 구현</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>구조·환경 설정</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>kiosk-customer 폴더 분리, API URL 환경변수화, 저장소 구조 정리</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>품질 관리</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>고객용 키오스크 자동 테스트 작성</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>고객용 키오스크 자동 테스트 작성(옵션카드 슬라이드 컴포넌트 포함), 결제 승인 재시도 안전 처리, 신규 기능 수동 테스트 체크리스트 작성, 저장소 정리(빌드 산출물 제거·줄바꿈 규칙 통일)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>요약: 고객용 키오스크의 프론트엔드 전 화면(홈·메뉴·장바구니·결제·주문완료)을 담당하고, 네이버페이·카카오페이·토스페이 결제 연동, 세트 메뉴·품절 로직, 다국어·반응형 대응, 자동 테스트를 수행함.</t>
-        </is>
-      </c>
+          <t>요약: 고객용 키오스크의 프론트엔드 전 화면(홈·메뉴·장바구니·결제·주문완료)을 담당하고, 네이버페이·카카오페이·토스페이 결제 연동, 세트 메뉴·품절 로직, 다국어·반응형 대응, 자동 테스트 및 결제 재시도 안전성 개선, 저장소 정리를 수행함.</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -274,10 +673,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="120" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -305,7 +710,7 @@
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="6">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -313,14 +718,14 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>고객용 키오스크 프로젝트를 초기화하고 홈·메뉴선택·장바구니·결제·주문완료 5개 화면의 기본 구조와 컴포넌트를 구현함.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -328,14 +733,14 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>장바구니 비어있음 검증과 결제 API 예외·타임아웃 처리를 추가하고 관리자 파일 정리, menuApi.js 통합, 홈 화면 디자인 작업에 착수함.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -343,14 +748,14 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>메뉴선택·장바구니·결제·주문완료 화면(SCR_002~005)의 디자인을 적용하고 메뉴 품절·빈 목록·빈 장바구니 상황에 대한 안내와 진입 차단 로직을 보완함.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -358,14 +763,14 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>메뉴 카테고리 사이드 메뉴와 슬라이드 화살표 UI를 추가하고, 총액 계산 로직 중복 제거, 90초 미사용 자동 초기화 및 안내 팝업, 장바구니 수량 표시 등 세부 로직을 정리함.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -373,14 +778,14 @@
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>결제 수단 선택 팝업(네이버페이/카카오페이/카드결제)을 추가하고 장바구니·결제내역 레이아웃과 영수증·주문번호 출력 버튼을 개선함.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -388,14 +793,14 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>고객용 키오스크를 kiosk-customer 폴더로 분리하고 README·gitignore·node_modules 등 저장소 구조를 정리했으며, 다국어(한/영) 지원과 화면 크기별 자동 스케일을 적용함.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="6">
+      <c r="A10" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -403,14 +808,14 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>메뉴·장바구니·결제 화면을 백엔드 API와 연동함.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -418,14 +823,14 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>결제 아키텍처 분리에 맞춰 프론트엔드 결제 연동을 재정비함.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="6">
+      <c r="A12" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -433,14 +838,14 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>주문 상태에 '결제대기'를 추가하고 결제 오류 유형별 처리 및 자동 재시도를 구현했으며, 미결제 주문 노출 방지와 장바구니 메뉴명 표시, 떡볶이 카드 CSS를 보완함.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="6">
+      <c r="A13" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -448,14 +853,14 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>장바구니 폰트 크기를 조정하고 네이버페이/카카오페이 QR 결제 모달을 추가함.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="6">
+      <c r="A14" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -463,14 +868,14 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>옵션 품절 시 카드에 품절 표시와 선택 차단 기능을 추가함.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="6">
+      <c r="A15" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -478,14 +883,14 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>결제 처리 중 뒤로가기로 인한 주문 취소를 차단하고, 세트 메뉴 구성품 품절 연동과 그룹 선택형 세트 메뉴 팝업·장바구니 연동을 구현함.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="6">
+      <c r="A16" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -493,14 +898,14 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>떡순튀세트 옵션(떡볶이맛/순대구성) 선택 기능과 토스페이 결제(키오스크 내 결제창 직접 호출)를 추가하고, API URL 환경변수화 및 결제수단 UI를 정리함.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="6">
+      <c r="A17" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -508,14 +913,14 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>토스/카카오 결제 취소 안내를 개선하고 confirm API 중복 호출을 방지했으며, 떡볶이 단품 맛 선택 기능을 구현함.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="6">
+      <c r="A18" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -523,27 +928,63 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>고객용 키오스크 자동 테스트를 추가하고 옵션 카드가 3개 이상일 때 슬라이드 가능하도록 UI를 개선함.</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>신규 기능(옵션카드 슬라이드) 수동 테스트 체크리스트를 작성해 전 항목을 검증하고, 잘못 커밋되어 있던 kiosk-customer/build 산출물을 저장소에서 정리함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>결제 승인 확인(confirm) 재시도 시 이미 완료된 결제가 오류로 처리되던 문제를 수정하고, 저장소 전반의 줄바꿈 규칙을 통일했으며, 옵션카드 슬라이드(DragScrollRow) 컴포넌트에 대한 자동 테스트를 추가함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:C18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C18"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -566,60 +1007,60 @@
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>자료 출처</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>고객용 키오스크(kiosk-customer) 프론트엔드 Git 커밋 기록</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>담당자 식별</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>박유진, Git 커밋 작성자 이메일 parkbori99@gmail.com 기준</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>작업일 계산</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>해당 이메일의 커밋이 확인되는 날짜를 중복 제거하여 계산</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>주의사항</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>커밋이 없는 기획·회의·검수 시간은 작업일 수에 포함되지 않을 수 있음</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>주요 기술</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>React, Axios, 네이버페이/카카오페이/토스페이 SDK</t>
         </is>

--- a/docs/박유진_분식집키오스크_작업일지.xlsx
+++ b/docs/박유진_분식집키오스크_작업일지.xlsx
@@ -1,46 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="날짜별 작업일지" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근거 및 참고" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="요약" sheetId="1" r:id="rId1"/>
+    <sheet name="날짜별 작업일지" sheetId="2" r:id="rId2"/>
+    <sheet name="근거 및 참고" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'날짜별 작업일지'!$A$3:$C$18</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <sz val="10"/>
       <name val="맑은 고딕"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="18"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
       <color rgb="FF555555"/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -58,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border/>
     <border>
       <left style="thin">
@@ -74,435 +69,44 @@
         <color rgb="FFD9D9D9"/>
       </bottom>
     </border>
-    <border>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="85" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
+    <col min="4" max="4" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -515,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 박유진 | 기간: 2026-07-13 ~ 2026-08-12</t>
+          <t>담당자: 박유진 | 기간: 2026-07-13 ~ 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -532,38 +136,38 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>총 커밋</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>89건</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>94건</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>작업 기간</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-13 ~ 2026-08-12 (31일)</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-13 ~ 2026-08-13 (32일)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>활동일</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>17일</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>18일</t>
         </is>
       </c>
     </row>
@@ -580,86 +184,83 @@
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>고객용 키오스크 프론트엔드</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>홈·메뉴선택·장바구니·결제·주문완료 5개 화면 구현 및 디자인, 다국어(한/영)·반응형 대응</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>결제 연동</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>네이버페이·카카오페이·토스페이 결제창 연동, 결제 오류 유형별 처리·자동 재시도, 결제 아키텍처 분리 대응</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>장바구니·주문 로직</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>수량 합산, 총액 계산 함수화, 빈 장바구니/빈 주문목록 안내 및 진입 차단, 90초 자동 초기화</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>메뉴·세트 옵션</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>메뉴·옵션 품절 처리, 세트 메뉴 구성품 품절 연동, 그룹 선택형 세트 메뉴 및 떡순튀세트 옵션 구현</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>구조·환경 설정</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>kiosk-customer 폴더 분리, API URL 환경변수화, 저장소 구조 정리</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>품질 관리</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>고객용 키오스크 자동 테스트 작성(옵션카드 슬라이드 컴포넌트 포함), 결제 승인 재시도 안전 처리, 신규 기능 수동 테스트 체크리스트 작성, 저장소 정리(빌드 산출물 제거·줄바꿈 규칙 통일)</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>고객용 키오스크 자동 테스트 작성, Playwright 기반 E2E 테스트(매장식사·포장·옵션·세트 메뉴) 구축</t>
         </is>
       </c>
     </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>요약: 고객용 키오스크의 프론트엔드 전 화면(홈·메뉴·장바구니·결제·주문완료)을 담당하고, 네이버페이·카카오페이·토스페이 결제 연동, 세트 메뉴·품절 로직, 다국어·반응형 대응, 자동 테스트 및 결제 재시도 안전성 개선, 저장소 정리를 수행함.</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="8" t="n"/>
+          <t>요약: 고객용 키오스크의 프론트엔드 전 화면(홈·메뉴·장바구니·결제·주문완료)을 담당하고, 네이버페이·카카오페이·토스페이 결제 연동, 세트 메뉴·품절 로직, 다국어·반응형 대응, 자동 테스트 및 Playwright E2E 테스트를 수행함.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -673,16 +274,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="120" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -710,7 +305,7 @@
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -718,14 +313,14 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>고객용 키오스크 프로젝트를 초기화하고 홈·메뉴선택·장바구니·결제·주문완료 5개 화면의 기본 구조와 컴포넌트를 구현함.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="6">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -733,14 +328,14 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>장바구니 비어있음 검증과 결제 API 예외·타임아웃 처리를 추가하고 관리자 파일 정리, menuApi.js 통합, 홈 화면 디자인 작업에 착수함.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -748,14 +343,14 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>메뉴선택·장바구니·결제·주문완료 화면(SCR_002~005)의 디자인을 적용하고 메뉴 품절·빈 목록·빈 장바구니 상황에 대한 안내와 진입 차단 로직을 보완함.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="6">
         <v>4</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -763,14 +358,14 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>메뉴 카테고리 사이드 메뉴와 슬라이드 화살표 UI를 추가하고, 총액 계산 로직 중복 제거, 90초 미사용 자동 초기화 및 안내 팝업, 장바구니 수량 표시 등 세부 로직을 정리함.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -778,14 +373,14 @@
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>결제 수단 선택 팝업(네이버페이/카카오페이/카드결제)을 추가하고 장바구니·결제내역 레이아웃과 영수증·주문번호 출력 버튼을 개선함.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -793,14 +388,14 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>고객용 키오스크를 kiosk-customer 폴더로 분리하고 README·gitignore·node_modules 등 저장소 구조를 정리했으며, 다국어(한/영) 지원과 화면 크기별 자동 스케일을 적용함.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="6">
         <v>7</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -808,14 +403,14 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>메뉴·장바구니·결제 화면을 백엔드 API와 연동함.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="6">
         <v>8</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -823,14 +418,14 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>결제 아키텍처 분리에 맞춰 프론트엔드 결제 연동을 재정비함.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -838,14 +433,14 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>주문 상태에 '결제대기'를 추가하고 결제 오류 유형별 처리 및 자동 재시도를 구현했으며, 미결제 주문 노출 방지와 장바구니 메뉴명 표시, 떡볶이 카드 CSS를 보완함.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="6">
         <v>10</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -853,14 +448,14 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>장바구니 폰트 크기를 조정하고 네이버페이/카카오페이 QR 결제 모달을 추가함.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -868,14 +463,14 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>옵션 품절 시 카드에 품절 표시와 선택 차단 기능을 추가함.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="6">
         <v>12</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -883,14 +478,14 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>결제 처리 중 뒤로가기로 인한 주문 취소를 차단하고, 세트 메뉴 구성품 품절 연동과 그룹 선택형 세트 메뉴 팝업·장바구니 연동을 구현함.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="6">
         <v>13</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -898,14 +493,14 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>떡순튀세트 옵션(떡볶이맛/순대구성) 선택 기능과 토스페이 결제(키오스크 내 결제창 직접 호출)를 추가하고, API URL 환경변수화 및 결제수단 UI를 정리함.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="6">
         <v>14</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -913,14 +508,14 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>토스/카카오 결제 취소 안내를 개선하고 confirm API 중복 호출을 방지했으며, 떡볶이 단품 맛 선택 기능을 구현함.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="6">
         <v>15</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -928,63 +523,72 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>고객용 키오스크 자동 테스트를 추가하고 옵션 카드가 3개 이상일 때 슬라이드 가능하도록 UI를 개선함.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="6">
         <v>16</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>신규 기능(옵션카드 슬라이드) 수동 테스트 체크리스트를 작성해 전 항목을 검증하고, 잘못 커밋되어 있던 kiosk-customer/build 산출물을 저장소에서 정리함.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="6">
         <v>17</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>결제 승인 확인(confirm) 재시도 시 이미 완료된 결제가 오류로 처리되던 문제를 수정하고, 저장소 전반의 줄바꿈 규칙을 통일했으며, 옵션카드 슬라이드(DragScrollRow) 컴포넌트에 대한 자동 테스트를 추가함.</t>
         </is>
       </c>
     </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="6">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>고객용 키오스크 E2E(Playwright) 테스트 환경을 구축하고 매장식사·포장·옵션 메뉴·세트 메뉴 담기부터 결제 완료까지의 흐름을 검증했으며, 테스트 코드를 Page Object Model 구조(tests/pages/fixtures)로 분리함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:C18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <autoFilter ref="A3:C21"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1007,60 +611,60 @@
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>자료 출처</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>고객용 키오스크(kiosk-customer) 프론트엔드 Git 커밋 기록</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>담당자 식별</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>박유진, Git 커밋 작성자 이메일 parkbori99@gmail.com 기준</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>작업일 계산</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>해당 이메일의 커밋이 확인되는 날짜를 중복 제거하여 계산</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>주의사항</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>커밋이 없는 기획·회의·검수 시간은 작업일 수에 포함되지 않을 수 있음</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>주요 기술</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>React, Axios, 네이버페이/카카오페이/토스페이 SDK</t>
         </is>

--- a/docs/박유진_분식집키오스크_작업일지.xlsx
+++ b/docs/박유진_분식집키오스크_작업일지.xlsx
@@ -119,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 박유진 | 기간: 2026-07-13 ~ 2026-08-13</t>
+          <t>담당자: 박유진 | 기간: 2026-07-13 ~ 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>94건</t>
+          <t>99건</t>
         </is>
       </c>
     </row>
@@ -155,7 +155,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13 ~ 2026-08-13 (32일)</t>
+          <t>2026-07-13 ~ 2026-08-25 (44일)</t>
         </is>
       </c>
     </row>
@@ -167,7 +167,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>18일</t>
+          <t>21일</t>
         </is>
       </c>
     </row>
@@ -255,10 +255,22 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>RTOS 연동 및 출력 처리</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>영수증/주문번호표 출력 요청(print_jobs) 프론트 연동, RTOS 폴링·완료 처리 흐름을 검증하는 백엔드 통합 테스트 작성</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>요약: 고객용 키오스크의 프론트엔드 전 화면(홈·메뉴·장바구니·결제·주문완료)을 담당하고, 네이버페이·카카오페이·토스페이 결제 연동, 세트 메뉴·품절 로직, 다국어·반응형 대응, 자동 테스트 및 Playwright E2E 테스트를 수행함.</t>
+          <t>요약: 고객용 키오스크의 프론트엔드 전 화면(홈·메뉴·장바구니·결제·주문완료)을 담당하고, 네이버페이·카카오페이·토스페이 결제 연동, 세트 메뉴·품절 로직, 다국어·반응형 대응, 자동 테스트 및 Playwright E2E 테스트를 수행했으며, 영수증/주문번호표 출력(print_jobs) 연동과 이를 검증하는 백엔드 통합 테스트도 수행함.</t>
         </is>
       </c>
     </row>
@@ -574,11 +586,56 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="6">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>주문완료 화면에 실제 order_id 기반 영수증/주문번호표 출력 요청(POST /api/print-jobs) 연동을 추가함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="6">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>RTOS 연동에 맞춰 주문 상태 저장(useOrderStore)과 메뉴·결제·토스결제 성공·주문완료 화면의 실시간 처리를 보완함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="6">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>출력 작업(print_jobs) 등록→RTOS 폴링→완료 처리 전체 흐름을 검증하는 백엔드 통합 테스트(PrintJobFlowIntegrationTest)를 추가하고, 영문 홈 화면의 Dine In/Take Out 버튼 줄바꿈을 띄어쓰기로 수정함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C21"/>
+  <autoFilter ref="A3:C24"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
